--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -462,9 +462,6 @@
           <t>第一版开发任务表使用说明</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -886,11 +883,15 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>b01 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -966,11 +967,15 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>b01 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1046,11 +1051,15 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>b01 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1126,11 +1135,15 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>b01 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1206,11 +1219,15 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>b02 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1286,11 +1303,15 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>b02 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1366,11 +1387,15 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>b02 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1446,11 +1471,15 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>b02 完成并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -11074,8 +11103,6 @@
           <t>约73~73</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -1555,11 +1555,15 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>b03 完成并通过验收（存档/随机/配置字段/诊断）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1635,11 +1639,15 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>b03 完成并通过验收（存档/随机/配置字段/诊断）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1715,11 +1723,15 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>b03 完成并通过验收（存档/随机/配置字段/诊断）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1795,11 +1807,15 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>b03 完成并通过验收（存档/随机/配置字段/诊断）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -1891,11 +1891,15 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>G0 集成验收通过：Launch→业务空场景(Home)→UI壳→表加载链路跑通；audit_framework_purity.py 通过；Home 登记进 BuildSettings（纯度审计加项目场景白名单）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -1975,11 +1975,15 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>蜂窝格棋盘数据模型（轴向坐标/六方向/边长n分档/合法格/分层）完成，Play Mode 验收 69/69 通过</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2055,11 +2059,15 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>棋子实体与占用层（零件/设施/任务标记/待维修对象基类，每格单实体，固定设施锁盘面）完成，Play Mode 验收 69/69 通过</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -2143,11 +2143,15 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>六相旋转与定势（左/右旋各一相位吸附，选定边=重力方向，旋转不改棋子）完成，Play Mode 验收 34/34 通过</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2223,11 +2227,15 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>拍击结算事务（扣拍→到期→下落→碰撞→FIFO→重力接续→拍末→稳定，SR-002/D-067）完成，Play Mode 验收 34/34 通过</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -2311,11 +2311,15 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>碰撞与触发语义（新碰撞判定/单次触发/静止相邻不重复/推落回新触发/原子事件）完成，Play Mode 验收 21/21 通过</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2391,11 +2395,15 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>FIFO 能力事件队列（事件入队/取出/即时结果，同对象同事件只处理一次，新触发入队尾）完成，Play Mode 验收 21/21 通过</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -2479,11 +2479,15 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>b08 验收通过(55/55)：撞锤/棘轮/线圈+公共维修能量/维修对象+计分体系</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2559,11 +2563,15 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>b08 验收通过(55/55)：撞锤/棘轮/线圈+公共维修能量/维修对象+计分体系</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2639,11 +2647,15 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>b08 验收通过(55/55)：撞锤/棘轮/线圈+公共维修能量/维修对象+计分体系</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -2731,11 +2731,15 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>b09 验收通过(31/31)：机械臂+轮关/过轮判定+种子复现+第一步预演</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2811,11 +2815,15 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>b09 验收通过(31/31)：机械臂+轮关/过轮判定+种子复现+第一步预演</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2891,11 +2899,15 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>b09 验收通过(31/31)：机械臂+轮关/过轮判定+种子复现+第一步预演</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2971,11 +2983,15 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>b09 验收通过(31/31)：机械臂+轮关/过轮判定+种子复现+第一步预演</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -3067,11 +3067,15 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>b10 验收通过(31/31)：盘面视图+棋子/设施/标记表现+操作循环UI+六分区HUD</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3147,11 +3151,15 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>b10 验收通过(31/31)：盘面视图+棋子/设施/标记表现+操作循环UI+六分区HUD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3227,11 +3235,15 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>b10 验收通过(31/31)：盘面视图+棋子/设施/标记表现+操作循环UI+六分区HUD</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3307,11 +3319,15 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>b10 验收通过(31/31)：盘面视图+棋子/设施/标记表现+操作循环UI+六分区HUD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -3403,11 +3403,15 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>b11 验收通过(25/25)：四选一框架+Buff数据结构与首批20项+暂停撤退菜单+关卡盘面配置表</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3483,11 +3487,15 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>b11 验收通过(25/25)：四选一框架+Buff数据结构与首批20项+暂停撤退菜单+关卡盘面配置表</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3563,11 +3571,15 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>b11 验收通过(25/25)：四选一框架+Buff数据结构与首批20项+暂停撤退菜单+关卡盘面配置表</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3643,11 +3655,15 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>b11 验收通过(25/25)：四选一框架+Buff数据结构与首批20项+暂停撤退菜单+关卡盘面配置表</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -3739,11 +3739,15 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>G1 盘面可玩验收门通过(19/19)：蜂窝格/旋转/碰撞连锁/FIFO/计分+维修能量/预演/教学三段样张/同种子/失败可读</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -3823,11 +3823,15 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>换向齿轮+铆合钳按条目接入并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3903,11 +3907,15 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>障碍8种(O-001~008)行为正确并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3983,11 +3991,15 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>棋盘异常8种区域注册与触发框架可配置化并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4063,11 +4075,15 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>任务标记锚点映射+特殊目标(到达/保持/顺序)判定可配置并通过验收</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -4159,11 +4159,15 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>Buff库20条配置化接入(叠加/上限/筛选)并接入结算生效</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4239,11 +4243,15 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>M类怪谈形态附着框架+M-012红舞鞋形态(宿主P-004/不占携带种类/改道路线)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -4327,11 +4327,15 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>准备页三区(关卡信息/两栏携带)纯逻辑模型+携带min(N,6)+关键件提示</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4407,11 +4411,15 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>关卡预览固定内容模型+逐轮轮配置读取(随机件不进入预览)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4487,11 +4495,15 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>初盘固定随机混合生成(固定元素+关键件固定位+携带池随机落位,同种子复现)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -4579,7 +4579,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>11 个 M 类图样来源挂接，按层级消耗普通/异常材料</t>
+          <t>15 个 M 类图样来源挂接，按层级消耗普通/异常材料</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R128"/>
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9946,89 +9946,87 @@
       <c r="R113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>ART-001</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ART-000</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>并行美术0 视觉样张</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>ART0 视觉样张</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>美术视觉</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>规范</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>UI 视觉规范与控件样张</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>色板/字体/九宫格/控件样张</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>占位资源</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>程序化占位资源生成（前置）</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>用脚本程序化生成占位图片并导入项目使用：盘面棋子/障碍/异常/任务标记/维修对象/零件20P/形态15M/UI图标；非运行时生成，产物为Assets下PNG，正式美术到位后逐项替换</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
         <is>
           <t>P0-013</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>ART0</t>
         </is>
       </c>
-      <c r="K114" s="2" t="n">
+      <c r="K114" t="n">
         <v>8</v>
       </c>
-      <c r="L114" s="2" t="n">
+      <c r="L114" t="n">
         <v>14</v>
       </c>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="N114" s="2" t="inlineStr">
-        <is>
-          <t>美术资源预算</t>
-        </is>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>视觉规范样张确认</t>
-        </is>
-      </c>
-      <c r="P114" s="2" t="inlineStr">
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>程序预算</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>占位PNG全套生成并导入，HexBoardView/EntityVisuals可引用，盘面与主要UI灰盒可视</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
         <is>
           <t>未开始</t>
         </is>
       </c>
-      <c r="Q114" s="2" t="inlineStr"/>
-      <c r="R114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ART-002</t>
+          <t>ART-001</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -10048,17 +10046,17 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>盘面</t>
+          <t>规范</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>六相定势盘视觉样张</t>
+          <t>UI 视觉规范与控件样张</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>盘框/蜂窝格/棋子/定势座/特效方向样张</t>
+          <t>色板/字体/九宫格/控件样张</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -10094,7 +10092,7 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>盘面视觉样张确认</t>
+          <t>视觉规范样张确认</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
@@ -10108,7 +10106,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ART-003</t>
+          <t>ART-002</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -10128,17 +10126,17 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>立绘</t>
+          <t>盘面</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>人物立绘样张</t>
+          <t>六相定势盘视觉样张</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>沈遥/周衡/居民模板状态差分样张</t>
+          <t>盘框/蜂窝格/棋子/定势座/特效方向样张</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -10174,7 +10172,7 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>立绘样张确认</t>
+          <t>盘面视觉样张确认</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
@@ -10188,7 +10186,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ART-004</t>
+          <t>ART-003</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -10208,17 +10206,17 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>立绘</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>场景背景样张</t>
+          <t>人物立绘样张</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>工作台/修理铺/舞蹈教室背景样张</t>
+          <t>沈遥/周衡/居民模板状态差分样张</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -10240,7 +10238,7 @@
         <v>8</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
@@ -10254,7 +10252,7 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>背景样张确认</t>
+          <t>立绘样张确认</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
@@ -10268,7 +10266,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ART-005</t>
+          <t>ART-004</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -10283,22 +10281,22 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>音画与文本</t>
+          <t>美术视觉</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>背景</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>音效方向样张</t>
+          <t>场景背景样张</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>咬合/拍击/连锁/维修完成音效风格样张</t>
+          <t>工作台/修理铺/舞蹈教室背景样张</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -10317,14 +10315,14 @@
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -10334,7 +10332,7 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>音效风格确认</t>
+          <t>背景样张确认</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
@@ -10348,37 +10346,37 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>ART-006</t>
+          <t>ART-005</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>并行美术1 批量制作</t>
+          <t>并行美术0 视觉样张</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ART1 批量制作</t>
+          <t>ART0 视觉样张</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>美术视觉</t>
+          <t>音画与文本</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>图标</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>零件与设施图</t>
+          <t>音效方向样张</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>20 P + 15 M + 8 O + 8 A + 维修对象/标记图</t>
+          <t>咬合/拍击/连锁/维修完成音效风格样张</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -10388,23 +10386,23 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>ART-002</t>
+          <t>P0-013</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>ART1</t>
+          <t>ART0</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -10414,7 +10412,7 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>全套图标完成</t>
+          <t>音效风格确认</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
@@ -10428,7 +10426,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ART-007</t>
+          <t>ART-006</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -10448,17 +10446,17 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>图标</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>UI 全套图标与九宫格</t>
+          <t>零件与设施图</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>全套控件、图标、九宫格资源</t>
+          <t>20 P + 15 M + 8 O + 8 A + 维修对象/标记图</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -10468,7 +10466,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>ART-001</t>
+          <t>ART-002</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -10494,7 +10492,7 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>UI 资源完成</t>
+          <t>全套图标完成</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
@@ -10508,7 +10506,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ART-008</t>
+          <t>ART-007</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -10528,17 +10526,17 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>立绘</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>立绘批量:首批人物差分</t>
+          <t>UI 全套图标与九宫格</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>首批人物立绘状态差分</t>
+          <t>全套控件、图标、九宫格资源</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -10548,7 +10546,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>ART-003</t>
+          <t>ART-001</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -10574,7 +10572,7 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>首批立绘完成</t>
+          <t>UI 资源完成</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
@@ -10588,7 +10586,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ART-009</t>
+          <t>ART-008</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -10608,17 +10606,17 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>立绘</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>背景批量:首发场景</t>
+          <t>立绘批量:首批人物差分</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>首发场景背景批量</t>
+          <t>首批人物立绘状态差分</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -10628,7 +10626,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>ART-004</t>
+          <t>ART-003</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -10654,7 +10652,7 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>首发背景完成</t>
+          <t>首批立绘完成</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
@@ -10668,7 +10666,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ART-010</t>
+          <t>ART-009</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -10688,17 +10686,17 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>动效</t>
+          <t>背景</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>盘面动效</t>
+          <t>背景批量:首发场景</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>旋转/咬合/拍击震波/连锁飘字动效</t>
+          <t>首发场景背景批量</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -10708,7 +10706,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>ART-002</t>
+          <t>ART-004</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -10717,10 +10715,10 @@
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -10734,7 +10732,7 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>盘面动效完成</t>
+          <t>首发背景完成</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
@@ -10748,7 +10746,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ART-011</t>
+          <t>ART-010</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -10763,22 +10761,22 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>音画与文本</t>
+          <t>美术视觉</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>动效</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>音效批量</t>
+          <t>盘面动效</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>全套音效批量制作</t>
+          <t>旋转/咬合/拍击震波/连锁飘字动效</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -10788,7 +10786,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>ART-005</t>
+          <t>ART-002</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -10797,14 +10795,14 @@
         </is>
       </c>
       <c r="K124" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -10814,7 +10812,7 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>音效完成</t>
+          <t>盘面动效完成</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
@@ -10828,7 +10826,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ART-012</t>
+          <t>ART-011</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -10848,17 +10846,17 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>音乐</t>
+          <t>音效</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>昼夜 BGM 与环境</t>
+          <t>音效批量</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>BGM 与环境音批量</t>
+          <t>全套音效批量制作</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -10880,7 +10878,7 @@
         <v>8</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -10894,7 +10892,7 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>BGM 完成</t>
+          <t>音效完成</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
@@ -10908,37 +10906,37 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ART-013</t>
+          <t>ART-012</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>并行美术2 集成验收</t>
+          <t>并行美术1 批量制作</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ART2 集成验收</t>
+          <t>ART1 批量制作</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>集成与验收</t>
+          <t>音画与文本</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>音乐</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>UI 视觉集成验收</t>
+          <t>昼夜 BGM 与环境</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>UI 视觉导入主工程验收</t>
+          <t>BGM 与环境音批量</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -10948,23 +10946,23 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>ART-007</t>
+          <t>ART-005</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>ART2</t>
+          <t>ART1</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -10974,7 +10972,7 @@
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>UI 集成通过</t>
+          <t>BGM 完成</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
@@ -10988,7 +10986,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ART-014</t>
+          <t>ART-013</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -11008,17 +11006,17 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>盘面</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>盘面与棋子视觉集成验收</t>
+          <t>UI 视觉集成验收</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>盘面/棋子视觉导入主工程验收</t>
+          <t>UI 视觉导入主工程验收</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -11028,7 +11026,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>ART-006,ART-010</t>
+          <t>ART-007</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
@@ -11054,7 +11052,7 @@
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>盘面集成通过</t>
+          <t>UI 集成通过</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
@@ -11068,7 +11066,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ART-015</t>
+          <t>ART-014</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -11088,17 +11086,17 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>音画</t>
+          <t>盘面</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>立绘/背景/音效集成验收</t>
+          <t>盘面与棋子视觉集成验收</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>立绘/背景/音效导入主工程验收</t>
+          <t>盘面/棋子视觉导入主工程验收</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -11108,7 +11106,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>ART-008,ART-009,ART-011,ART-012</t>
+          <t>ART-006,ART-010</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -11134,7 +11132,7 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>音画集成通过</t>
+          <t>盘面集成通过</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
@@ -11144,6 +11142,86 @@
       </c>
       <c r="Q128" s="2" t="inlineStr"/>
       <c r="R128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>ART-015</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>并行美术2 集成验收</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>ART2 集成验收</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>集成与验收</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>音画</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>立绘/背景/音效集成验收</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>立绘/背景/音效导入主工程验收</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>ART-008,ART-009,ART-011,ART-012</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>ART2</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>美术资源预算</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>音画集成通过</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr"/>
+      <c r="R129" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R128"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>用脚本程序化生成占位图片并导入项目使用：盘面棋子/障碍/异常/任务标记/维修对象/零件20P/形态15M/UI图标；非运行时生成，产物为Assets下PNG，正式美术到位后逐项替换</t>
+          <t>用脚本程序化生成占位图片并导入项目，覆盖所有可占位的美术资源：盘面棋子/障碍/异常/任务标记/维修对象/零件20P/形态15M/UI界面素材（图标/按钮/面板/页签）/其它对象；非运行时生成，产物为Assets下PNG；生成时不止简单几何图形，带渐变/描边/纹理等基础效果；正式美术到位后逐项替换</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>占位PNG全套生成并导入，HexBoardView/EntityVisuals可引用，盘面与主要UI灰盒可视</t>
+          <t>全套占位PNG生成并导入（盘面+UI+其它对象），带基础效果（渐变/描边/纹理），可供HexBoardView/EntityVisuals/UI引用，盘面与主要UI灰盒可视</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R129"/>
+  <dimension ref="A1:R130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11223,6 +11223,84 @@
       <c r="Q129" s="2" t="inlineStr"/>
       <c r="R129" s="2" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>INT-001</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>流程接入</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>流程接入</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>集成与验收</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>流程接入</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>全量流程接入</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>把 b01~b27 已实现的全部业务内容（盘面结算/事件/任务/地图/存档/经济/工作台/图鉴/序章/供给等）接入正式运行流程（场景/UIForm 宿主与导航/输入驱动/游戏循环），使游戏在 Editor 中可实际游玩。分四步递进：UI 框架接线→盘面可玩→一天闭环→成长闭环。</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>P4-007</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>44</v>
+      </c>
+      <c r="L130" t="n">
+        <v>70</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>程序预算</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>全部已实现功能接入正式运行流程，Editor 运行可实际游玩并通过运行验收（仅探针不算通过）；每步接入后必须运行验证通过。</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>拆四步见《分批开发执行计划》流程接入节；验收标准按 2026-09-21 新增规则「接入正式流程+验收通过」执行。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -11292,12 +11292,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>拆四步见《分批开发执行计划》流程接入节；验收标准按 2026-09-21 新增规则「接入正式流程+验收通过」执行。</t>
+          <t>拆四步见《分批开发执行计划》流程接入节；验收标准按 2026-09-21 新增规则「接入正式流程+验收通过」执行。b41（UI框架接线）/b42（盘面可玩）/b43（一天闭环）已通过运行验收；b44（成长闭环）剩余。</t>
         </is>
       </c>
     </row>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -7459,7 +7459,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -7619,7 +7619,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -8019,7 +8019,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -8099,7 +8099,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -8739,7 +8739,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9059,7 +9059,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9219,7 +9219,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr"/>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr"/>
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9459,7 +9459,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr"/>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr"/>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9699,7 +9699,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr"/>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr"/>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr"/>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -9863,7 +9863,11 @@
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr"/>
-      <c r="R112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>G6后补全：P-005~020 全部行为数值实装（b45~b47，超出首发清单范围）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -5139,11 +5139,17 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>b48 已实现 LevelCalibrationRunner：批量跑种子统计通过率/拍数分布（卷帘门 24 种子：纯拍击 0%、机械臂预置 29.2%）</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -10029,7 +10029,15 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>4</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>b49 已补齐：占位 PNG 全套 59 项（20P+15M+8O+8A+2 标记+6 UI），渐变/描边/高光/纹理，正式美术到位后逐项替换</t>
         </is>
       </c>
     </row>

--- a/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/10-开发计划/第一版开发任务表.xlsx
@@ -10115,11 +10115,15 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr"/>
-      <c r="R115" s="2" t="inlineStr"/>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>b51 已出 UI 视觉规范与控件样张草案（Docs/GameDesign/11-美术规范/），待视觉方向确认</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10195,11 +10199,15 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr"/>
-      <c r="R116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>b51 已出六相定势盘视觉规范与盘面样张草案，待视觉方向确认</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
